--- a/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_64981_completo.xlsx
+++ b/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_64981_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf7f6cc127c384480"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd6341b02d7fc4bb7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,141 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3410</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4258</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5023</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5524</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5695</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5671</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4500</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5556</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3580</x:v>
+        <x:v>      2.5984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2198</x:v>
+        <x:v>      2.5279</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.2489</x:v>
+        <x:v>      2.5224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3176</x:v>
+        <x:v>      2.5811</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3275</x:v>
+        <x:v>      2.5896</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4382</x:v>
+        <x:v>      2.6848</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.3682</x:v>
+        <x:v>      2.6246</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4366</x:v>
+        <x:v>      2.6834</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4161</x:v>
+        <x:v>      2.6658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +534,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5201</x:v>
+        <x:v>      2.7553</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +549,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.5601</x:v>
+        <x:v>      2.7899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +564,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.4890</x:v>
+        <x:v>      2.7285</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +579,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.6215</x:v>
+        <x:v>      2.8430</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7435</x:v>
+        <x:v>      2.9488</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +609,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8545</x:v>
+        <x:v>      3.0453</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +624,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7774</x:v>
+        <x:v>      2.9782</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +639,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8894</x:v>
+        <x:v>      3.0758</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8972</x:v>
+        <x:v>      3.0825</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9688</x:v>
+        <x:v>      3.1450</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.0130</x:v>
+        <x:v>      3.1836</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9846</x:v>
+        <x:v>      3.1587</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8817</x:v>
+        <x:v>      3.0690</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +729,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8082</x:v>
+        <x:v>      3.0050</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +744,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.7929</x:v>
+        <x:v>      2.9917</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +759,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8177</x:v>
+        <x:v>      3.0475</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9012</x:v>
+        <x:v>      3.0860</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +789,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8976</x:v>
+        <x:v>      3.0829</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9333</x:v>
+        <x:v>      3.1140</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_64981_completo.xlsx
+++ b/13774_Cuenca_Jequetepeque/_raw_reportes_xlsx/IDConfig_64981_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd6341b02d7fc4bb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3ebde355c0e34094"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.1931</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.9829</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      3.0738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4776</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2006</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1690</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4507</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3700</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4746</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5679</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6488</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.6316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8197</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.7567</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.5464</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2110</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3237</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0091</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.9515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1521</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2884</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2594</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3053</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2547</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1787</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2211</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2329</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3107</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3155</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2057</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1713</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1347</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1425</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0253</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0025</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0188</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.0474</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1305</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1909</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.3868</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4529</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.4804</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2055</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.1931</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.2388</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.3410</x:v>
+        <x:v>      2.3413</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -279,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4258</x:v>
+        <x:v>      2.4261</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5023</x:v>
+        <x:v>      2.5025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5524</x:v>
+        <x:v>      2.5527</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5695</x:v>
+        <x:v>      2.5698</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5671</x:v>
+        <x:v>      2.5674</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.4500</x:v>
+        <x:v>      2.4502</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5646</x:v>
+        <x:v>      2.5299</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5556</x:v>
+        <x:v>      2.5559</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5984</x:v>
+        <x:v>      2.5987</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5279</x:v>
+        <x:v>      2.4951</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5224</x:v>
+        <x:v>      2.5226</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5811</x:v>
+        <x:v>      2.5814</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.5896</x:v>
+        <x:v>      2.5899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6848</x:v>
+        <x:v>      2.6851</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6246</x:v>
+        <x:v>      2.6248</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6834</x:v>
+        <x:v>      2.6837</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.6658</x:v>
+        <x:v>      2.6661</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7553</x:v>
+        <x:v>      2.7556</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7899</x:v>
+        <x:v>      2.7902</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.7285</x:v>
+        <x:v>      2.7288</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.8430</x:v>
+        <x:v>      2.8433</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.9488</x:v>
+        <x:v>      2.9491</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0453</x:v>
+        <x:v>      3.0456</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.9782</x:v>
+        <x:v>      2.9785</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0758</x:v>
+        <x:v>      3.0761</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0825</x:v>
+        <x:v>      3.0828</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1450</x:v>
+        <x:v>      3.1453</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1836</x:v>
+        <x:v>      3.1840</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1587</x:v>
+        <x:v>      3.1591</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0690</x:v>
+        <x:v>      3.0693</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0050</x:v>
+        <x:v>      3.0053</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      2.9917</x:v>
+        <x:v>      2.9920</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0475</x:v>
+        <x:v>      3.0090</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0860</x:v>
+        <x:v>      3.0863</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.0829</x:v>
+        <x:v>      3.0832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.1140</x:v>
+        <x:v>      3.1143</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9886</x:v>
+        <x:v>      3.1626</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1201</x:v>
+        <x:v>      3.2797</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1334</x:v>
+        <x:v>      3.2895</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1059</x:v>
+        <x:v>      3.2657</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.8776</x:v>
+        <x:v>      3.0658</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9966</x:v>
+        <x:v>      3.1697</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9327</x:v>
+        <x:v>      3.1138</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9014</x:v>
+        <x:v>      3.0866</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      3.9779</x:v>
+        <x:v>      3.1529</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.1087</x:v>
+        <x:v>      3.2678</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3424</x:v>
+        <x:v>      3.4739</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4558</x:v>
+        <x:v>      3.5738</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3014</x:v>
+        <x:v>      3.4371</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.3623</x:v>
+        <x:v>      3.4909</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4510</x:v>
+        <x:v>      3.5691</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5049</x:v>
+        <x:v>      3.6168</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.4732</x:v>
+        <x:v>      3.5888</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.5142</x:v>
+        <x:v>      3.6251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.6348</x:v>
+        <x:v>      3.7320</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8049</x:v>
+        <x:v>      3.8832</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8000</x:v>
+        <x:v>      3.8788</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.7326</x:v>
+        <x:v>      3.8190</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8437</x:v>
+        <x:v>      3.9179</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9174</x:v>
+        <x:v>      4.7115</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.8585</x:v>
+        <x:v>      4.5497</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9172</x:v>
+        <x:v>      4.7109</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      4.9821</x:v>
+        <x:v>      4.8890</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0885</x:v>
+        <x:v>      5.1302</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0731</x:v>
+        <x:v>      5.1383</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.0569</x:v>
+        <x:v>      5.0940</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1581</x:v>
+        <x:v>      5.3510</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1140</x:v>
+        <x:v>      5.2500</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1323</x:v>
+        <x:v>      5.3000</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1325</x:v>
+        <x:v>      5.2984</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1298</x:v>
+        <x:v>      5.2930</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      5.1812</x:v>
+        <x:v>      5.1517</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.7493</x:v>
+        <x:v>      7.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.7689</x:v>
+        <x:v>      8.4978</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>     14.8203</x:v>
+        <x:v>     14.6509</x:v>
       </x:c>
     </x:row>
     <x:row>
